--- a/artfynd/A 65382-2021 artfynd.xlsx
+++ b/artfynd/A 65382-2021 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119506835</v>
+        <v>119506853</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,38 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541636</v>
+        <v>541641</v>
       </c>
       <c r="R3" t="n">
-        <v>7246866</v>
+        <v>7246887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,22 +886,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Granlågor</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlågor</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119506853</v>
+        <v>119506835</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,34 +930,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541641</v>
+        <v>541636</v>
       </c>
       <c r="R4" t="n">
-        <v>7246887</v>
+        <v>7246866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,17 +1007,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Granlågor</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # Granlågor</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 65382-2021 artfynd.xlsx
+++ b/artfynd/A 65382-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119506819</v>
+        <v>119506835</v>
       </c>
       <c r="B2" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541633</v>
+        <v>541636</v>
       </c>
       <c r="R2" t="n">
-        <v>7246883</v>
+        <v>7246866</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,12 +773,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlågor</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlågor</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,37 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119506853</v>
+        <v>119506880</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,7 +831,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541641</v>
+        <v>541599</v>
       </c>
       <c r="R3" t="n">
         <v>7246887</v>
@@ -886,17 +880,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granlåga, grov</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # Granlåga, grov</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119506835</v>
+        <v>119506819</v>
       </c>
       <c r="B4" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,38 +924,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541636</v>
+        <v>541633</v>
       </c>
       <c r="R4" t="n">
-        <v>7246866</v>
+        <v>7246883</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,12 +1007,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Granlågor</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlågor</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1037,6 +1027,576 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119506822</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>541602</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7246889</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Granlåga grov</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga grov</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119506842</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>541629</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7246917</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119506852</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>541629</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7246933</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119506853</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>541641</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7246887</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119506854</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>541634</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7246902</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
